--- a/public/templates/test_input/baocaocongtruong_khaithac_20.xlsx
+++ b/public/templates/test_input/baocaocongtruong_khaithac_20.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="0" windowWidth="18795" windowHeight="10905" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>CT Khai thác 1</t>
+          <t>Khai thác 5</t>
         </is>
       </c>
       <c r="C5" s="69" t="n">
@@ -10275,24 +10275,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:AC1"/>
     <mergeCell ref="D5:D7"/>
+    <mergeCell ref="H5:H7"/>
     <mergeCell ref="W3:Y3"/>
     <mergeCell ref="I2:M2"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="T3:V3"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="Z3:AB3"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F5:F7"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="E5:E7"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="P3:R3"/>
     <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
